--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-10/2025-07-16</t>
+          <t>multi-venue - Sales Summary - 2025-07-13/2025-07-19</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22110.65</v>
+        <v>22716.37</v>
       </c>
       <c r="C3" t="n">
-        <v>22110.65</v>
+        <v>22716.37</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18836.93</v>
+        <v>18616.68</v>
       </c>
       <c r="C4" t="n">
-        <v>18836.93</v>
+        <v>18616.68</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25467.4</v>
+        <v>26539.37</v>
       </c>
       <c r="C5" t="n">
-        <v>25467.4</v>
+        <v>26539.37</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15399.45</v>
+        <v>15500.88</v>
       </c>
       <c r="C6" t="n">
-        <v>15399.45</v>
+        <v>15500.88</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4894.99</v>
+        <v>2814.47</v>
       </c>
       <c r="C7" t="n">
-        <v>4894.99</v>
+        <v>2814.47</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8249.309999999999</v>
+        <v>8590.49</v>
       </c>
       <c r="C8" t="n">
-        <v>8249.309999999999</v>
+        <v>8590.49</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94958.73000000001</v>
+        <v>94778.26000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>94958.73000000001</v>
+        <v>94778.26000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-13/2025-07-19</t>
+          <t>multi-venue - Sales Summary - 2025-07-20/2025-07-26</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22716.37</v>
+        <v>24348.45</v>
       </c>
       <c r="C3" t="n">
-        <v>22716.37</v>
+        <v>24348.45</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1508</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18616.68</v>
+        <v>18719.53</v>
       </c>
       <c r="C4" t="n">
-        <v>18616.68</v>
+        <v>18719.53</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1182</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26539.37</v>
+        <v>30163.73</v>
       </c>
       <c r="C5" t="n">
-        <v>26539.37</v>
+        <v>30163.73</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1726</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15500.88</v>
+        <v>15717.48</v>
       </c>
       <c r="C6" t="n">
-        <v>15500.88</v>
+        <v>15717.48</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>901</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2814.47</v>
+        <v>5257.07</v>
       </c>
       <c r="C7" t="n">
-        <v>2814.47</v>
+        <v>5257.07</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>247</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8590.49</v>
+        <v>8348.5</v>
       </c>
       <c r="C8" t="n">
-        <v>8590.49</v>
+        <v>8348.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>437</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94778.26000000001</v>
+        <v>102554.76</v>
       </c>
       <c r="C9" t="n">
-        <v>94778.26000000001</v>
+        <v>102554.76</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-20/2025-07-26</t>
+          <t>multi-venue - Sales Summary - 2025-07-27/2025-08-02</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24348.45</v>
+        <v>24463.07</v>
       </c>
       <c r="C3" t="n">
-        <v>24348.45</v>
+        <v>24463.07</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1558</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18719.53</v>
+        <v>20976.23</v>
       </c>
       <c r="C4" t="n">
-        <v>18719.53</v>
+        <v>20976.23</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1209</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30163.73</v>
+        <v>29902.2</v>
       </c>
       <c r="C5" t="n">
-        <v>30163.73</v>
+        <v>29902.2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1895</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15717.48</v>
+        <v>18281.01</v>
       </c>
       <c r="C6" t="n">
-        <v>15717.48</v>
+        <v>18281.01</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1004</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5257.07</v>
+        <v>7161.43</v>
       </c>
       <c r="C7" t="n">
-        <v>5257.07</v>
+        <v>7161.43</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>450</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8348.5</v>
+        <v>9365.57</v>
       </c>
       <c r="C8" t="n">
-        <v>8348.5</v>
+        <v>9365.57</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>493</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102554.76</v>
+        <v>110149.51</v>
       </c>
       <c r="C9" t="n">
-        <v>102554.76</v>
+        <v>110149.51</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-07-27/2025-08-02</t>
+          <t>multi-venue - Sales Summary - 2025-08-03/2025-08-09</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24463.07</v>
+        <v>24909.16</v>
       </c>
       <c r="C3" t="n">
-        <v>24463.07</v>
+        <v>24909.16</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1595</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20976.23</v>
+        <v>16959.39</v>
       </c>
       <c r="C4" t="n">
-        <v>20976.23</v>
+        <v>16959.39</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1279</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29902.2</v>
+        <v>28884.17</v>
       </c>
       <c r="C5" t="n">
-        <v>29902.2</v>
+        <v>28884.17</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1912</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18281.01</v>
+        <v>17067.37</v>
       </c>
       <c r="C6" t="n">
-        <v>18281.01</v>
+        <v>17067.37</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1036</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7161.43</v>
+        <v>5220</v>
       </c>
       <c r="C7" t="n">
-        <v>7161.43</v>
+        <v>5220</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>625</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9365.57</v>
+        <v>8225.809999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>9365.57</v>
+        <v>8225.809999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>477</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110149.51</v>
+        <v>101265.9</v>
       </c>
       <c r="C9" t="n">
-        <v>110149.51</v>
+        <v>101265.9</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-03/2025-08-09</t>
+          <t>multi-venue - Sales Summary - 2025-08-10/2025-08-16</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24909.16</v>
+        <v>19672.47</v>
       </c>
       <c r="C3" t="n">
-        <v>24909.16</v>
+        <v>19672.47</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1630</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16959.39</v>
+        <v>18615.61</v>
       </c>
       <c r="C4" t="n">
-        <v>16959.39</v>
+        <v>18615.61</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1086</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28884.17</v>
+        <v>24550.71</v>
       </c>
       <c r="C5" t="n">
-        <v>28884.17</v>
+        <v>24550.71</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1835</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17067.37</v>
+        <v>18139.24</v>
       </c>
       <c r="C6" t="n">
-        <v>17067.37</v>
+        <v>18139.24</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5220</v>
+        <v>5337.36</v>
       </c>
       <c r="C7" t="n">
-        <v>5220</v>
+        <v>5337.36</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8225.809999999999</v>
+        <v>7399.2</v>
       </c>
       <c r="C8" t="n">
-        <v>8225.809999999999</v>
+        <v>7399.2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>458</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101265.9</v>
+        <v>93714.59</v>
       </c>
       <c r="C9" t="n">
-        <v>101265.9</v>
+        <v>93714.59</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-10/2025-08-16</t>
+          <t>multi-venue - Sales Summary - 2025-08-17/2025-08-23</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19672.47</v>
+        <v>18757.06</v>
       </c>
       <c r="C3" t="n">
-        <v>19672.47</v>
+        <v>18757.06</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1351</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18615.61</v>
+        <v>19220.45</v>
       </c>
       <c r="C4" t="n">
-        <v>18615.61</v>
+        <v>19220.45</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1184</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24550.71</v>
+        <v>22599.22</v>
       </c>
       <c r="C5" t="n">
-        <v>24550.71</v>
+        <v>22599.22</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1634</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18139.24</v>
+        <v>11977.74</v>
       </c>
       <c r="C6" t="n">
-        <v>18139.24</v>
+        <v>11977.74</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>985</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5337.36</v>
+        <v>4417.88</v>
       </c>
       <c r="C7" t="n">
-        <v>5337.36</v>
+        <v>4417.88</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>460</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7399.2</v>
+        <v>6704.76</v>
       </c>
       <c r="C8" t="n">
-        <v>7399.2</v>
+        <v>6704.76</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>423</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93714.59</v>
+        <v>83677.11</v>
       </c>
       <c r="C9" t="n">
-        <v>93714.59</v>
+        <v>83677.11</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-17/2025-08-23</t>
+          <t>multi-venue - Sales Summary - 2025-08-24/2025-08-30</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18757.06</v>
+        <v>16420.37</v>
       </c>
       <c r="C3" t="n">
-        <v>18757.06</v>
+        <v>16420.37</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1296</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19220.45</v>
+        <v>17626.08</v>
       </c>
       <c r="C4" t="n">
-        <v>19220.45</v>
+        <v>17626.08</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1199</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22599.22</v>
+        <v>21712.51</v>
       </c>
       <c r="C5" t="n">
-        <v>22599.22</v>
+        <v>21712.51</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1556</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11977.74</v>
+        <v>11616.48</v>
       </c>
       <c r="C6" t="n">
-        <v>11977.74</v>
+        <v>11616.48</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>773</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4417.88</v>
+        <v>4885.46</v>
       </c>
       <c r="C7" t="n">
-        <v>4417.88</v>
+        <v>4885.46</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>398</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6704.76</v>
+        <v>5573.32</v>
       </c>
       <c r="C8" t="n">
-        <v>6704.76</v>
+        <v>5573.32</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>388</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83677.11</v>
+        <v>77834.22</v>
       </c>
       <c r="C9" t="n">
-        <v>83677.11</v>
+        <v>77834.22</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-24/2025-08-30</t>
+          <t>multi-venue - Sales Summary - 2025-08-31/2025-09-06</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16420.37</v>
+        <v>18312.3</v>
       </c>
       <c r="C3" t="n">
-        <v>16420.37</v>
+        <v>18312.3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1162</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17626.08</v>
+        <v>16110.77</v>
       </c>
       <c r="C4" t="n">
-        <v>17626.08</v>
+        <v>16110.77</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1122</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21712.51</v>
+        <v>20974.27</v>
       </c>
       <c r="C5" t="n">
-        <v>21712.51</v>
+        <v>20974.27</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1469</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11616.48</v>
+        <v>15329.22</v>
       </c>
       <c r="C6" t="n">
-        <v>11616.48</v>
+        <v>15329.22</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>761</v>
+        <v>862</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4885.46</v>
+        <v>4435.9</v>
       </c>
       <c r="C7" t="n">
-        <v>4885.46</v>
+        <v>4435.9</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>415</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5573.32</v>
+        <v>6876.4</v>
       </c>
       <c r="C8" t="n">
-        <v>5573.32</v>
+        <v>6876.4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77834.22</v>
+        <v>82038.85999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>77834.22</v>
+        <v>82038.85999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
